--- a/countries/se-z/2026-2029.xlsx
+++ b/countries/se-z/2026-2029.xlsx
@@ -59416,10 +59416,10 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U418" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16">
